--- a/ARM Functions/Other Mechanics/Move Alternate Animations Mine.xlsx
+++ b/ARM Functions/Other Mechanics/Move Alternate Animations Mine.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Other Mechanics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F60CBB-804A-4558-B6E8-D232723EAC01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{433F565F-4F72-461B-BE80-D84816DD965B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16457" yWindow="0" windowWidth="16457" windowHeight="17914" activeTab="1" xr2:uid="{664BA6B8-043A-4EF3-A83B-BDEF02BD0490}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16457" windowHeight="17914" activeTab="1" xr2:uid="{664BA6B8-043A-4EF3-A83B-BDEF02BD0490}"/>
   </bookViews>
   <sheets>
     <sheet name="new function" sheetId="4" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="list of stock moves" sheetId="6" r:id="rId3"/>
     <sheet name="Original" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="191029" iterate="1" iterateCount="5"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1626" uniqueCount="1349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1627" uniqueCount="1349">
   <si>
     <t>notes</t>
   </si>
@@ -3969,9 +3969,6 @@
     <t>3) Make 4 new relocation patch entries to write the 4 offsets to the addresses in the indicated slots at the end of the function</t>
   </si>
   <si>
-    <t>offset to end of special sequences, set this manually</t>
-  </si>
-  <si>
     <t>3C002DE9</t>
   </si>
   <si>
@@ -4062,9 +4059,6 @@
     <t>B200D2E1</t>
   </si>
   <si>
-    <t>B5010000</t>
-  </si>
-  <si>
     <t>Ultima Cannon</t>
   </si>
   <si>
@@ -4074,12 +4068,6 @@
     <t>D504</t>
   </si>
   <si>
-    <t>4250A003</t>
-  </si>
-  <si>
-    <t>439 = 0x1B7</t>
-  </si>
-  <si>
     <t>Electro Shot</t>
   </si>
   <si>
@@ -4104,10 +4092,22 @@
     <t>AF02</t>
   </si>
   <si>
-    <t>F303</t>
-  </si>
-  <si>
     <t>00144F50</t>
+  </si>
+  <si>
+    <t>Mega, Pulverizing Pancake</t>
+  </si>
+  <si>
+    <t>offset to end of special sequences, set this manually, enter dec final file</t>
+  </si>
+  <si>
+    <t>4650A003</t>
+  </si>
+  <si>
+    <t>D804</t>
+  </si>
+  <si>
+    <t>D904</t>
   </si>
 </sst>
 </file>
@@ -4602,7 +4602,7 @@
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1276</v>
@@ -4614,7 +4614,7 @@
         <v>0007762C</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>1253</v>
@@ -4629,7 +4629,7 @@
         <v>00077630</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>1254</v>
@@ -4701,7 +4701,7 @@
         <v>00077644</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="C10" s="10" t="str">
         <f>_xlfn.CONCAT("b 0x",A36)</f>
@@ -4730,7 +4730,7 @@
         <v>0007764C</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="C12" s="6" t="str">
         <f>_xlfn.CONCAT("bhs 0x",A18)</f>
@@ -4746,7 +4746,7 @@
         <v>00077650</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>1288</v>
@@ -4761,7 +4761,7 @@
         <v>00077654</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="C14" s="3" t="str">
         <f>_xlfn.CONCAT("bls 0x",A36)</f>
@@ -4777,7 +4777,7 @@
         <v>00077658</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="C15" s="3" t="str">
         <f>_xlfn.CONCAT("ldrhi r0, [pc, #",HEX2DEC(A41)-HEX2DEC(A15)-8,"]")</f>
@@ -4793,7 +4793,7 @@
         <v>0007765C</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>1290</v>
@@ -4808,7 +4808,7 @@
         <v>00077660</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="C17" s="3" t="str">
         <f>_xlfn.CONCAT("b 0x",A$39)</f>
@@ -4824,7 +4824,7 @@
         <v>00077664</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="C18" s="6" t="str">
         <f>_xlfn.CONCAT("ldreq r3, [pc, #",HEX2DEC(A42)-HEX2DEC(A18)-8,"]")</f>
@@ -4840,11 +4840,11 @@
         <v>00077668</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>1337</v>
+        <v>1346</v>
       </c>
       <c r="C19" s="6" t="str">
         <f>_xlfn.CONCAT("moveq r5, 0x",_xlfn.XLOOKUP(VALUE(MID(D18,4,1)),'Table Builder'!H:H,'Table Builder'!O:O))</f>
-        <v>moveq r5, 0x45</v>
+        <v>moveq r5, 0x46</v>
       </c>
       <c r="D19" s="6"/>
     </row>
@@ -4854,7 +4854,7 @@
         <v>0007766C</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="C20" s="6" t="str">
         <f>_xlfn.CONCAT("beq 0x",A28)</f>
@@ -4883,7 +4883,7 @@
         <v>00077674</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="C22" s="6" t="str">
         <f>_xlfn.CONCAT("ldrlo r3, [pc, #",HEX2DEC(A43)-HEX2DEC(A22)-8,"]")</f>
@@ -4899,7 +4899,7 @@
         <v>00077678</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="C23" s="6" t="str">
         <f>_xlfn.CONCAT("movlo r5, 0x",_xlfn.XLOOKUP(VALUE(MID(D22,4,1)),'Table Builder'!H:H,'Table Builder'!O:O))</f>
@@ -4913,7 +4913,7 @@
         <v>0007767C</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="C24" s="6" t="str">
         <f>_xlfn.CONCAT("ldreq r3, [pc, #",HEX2DEC(A44)-HEX2DEC(A24)-8,"]")</f>
@@ -4931,7 +4931,7 @@
         <v>00077680</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="C25" s="6" t="str">
         <f>_xlfn.CONCAT("moveq r5, 0x",_xlfn.XLOOKUP(VALUE(MID(D24,4,1)),'Table Builder'!H:H,'Table Builder'!O:O))</f>
@@ -4947,7 +4947,7 @@
         <v>00077684</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="C26" s="6" t="str">
         <f>_xlfn.CONCAT("ldrhi r3, [pc, #",HEX2DEC(A45)-HEX2DEC(A26)-8,"]")</f>
@@ -4965,7 +4965,7 @@
         <v>00077688</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="C27" s="6" t="str">
         <f>_xlfn.CONCAT("movhi r5, 0x",_xlfn.XLOOKUP(VALUE(MID(D26,4,1)),'Table Builder'!H:H,'Table Builder'!O:O))</f>
@@ -4981,7 +4981,7 @@
         <v>0007768C</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>1274</v>
@@ -4998,13 +4998,13 @@
         <v>00077690</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="C29" s="8" t="s">
+        <v>1327</v>
+      </c>
+      <c r="D29" s="8" t="s">
         <v>1328</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>1329</v>
       </c>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
@@ -5015,7 +5015,7 @@
         <v>00077694</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>1277</v>
@@ -5048,7 +5048,7 @@
         <v>0007769C</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="C32" s="8" t="str">
         <f>_xlfn.CONCAT("beq 0x",A38)</f>
@@ -5064,7 +5064,7 @@
         <v>000776A0</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>1281</v>
@@ -5077,7 +5077,7 @@
         <v>000776A4</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>1282</v>
@@ -5092,7 +5092,7 @@
         <v>000776A8</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="C35" s="8" t="str">
         <f>_xlfn.CONCAT("blo 0x",A29)</f>
@@ -5137,10 +5137,10 @@
         <v>000776B4</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>1286</v>
@@ -5152,7 +5152,7 @@
         <v>000776B8</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="C39" s="1" t="str">
         <f>SUBSTITUTE(C3,"push","pop")</f>
@@ -5176,14 +5176,15 @@
         <f t="shared" si="0"/>
         <v>000776C0</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>1333</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>1338</v>
+      <c r="B41" s="1" t="str">
+        <f>_xlfn.LET(_xlpm.x,DEC2HEX(C41-800,4),RIGHT(_xlpm.x,2)&amp;LEFT(_xlpm.x,2)&amp;REPT(0,4))</f>
+        <v>B9010000</v>
+      </c>
+      <c r="C41" s="1">
+        <v>1241</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>1302</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -5243,7 +5244,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F350D40E-C5C1-4F0A-9BA0-EE14E6CE8D22}">
-  <dimension ref="A1:O81"/>
+  <dimension ref="A1:O82"/>
   <sheetFormatPr defaultRowHeight="14.15"/>
   <cols>
     <col min="1" max="1" width="6.35546875" bestFit="1" customWidth="1"/>
@@ -5360,30 +5361,30 @@
       </c>
       <c r="I3">
         <f>COUNTIF(D:D,"="&amp;H3)</f>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J3" s="19" t="str" cm="1">
         <f t="array" ref="J3">_xlfn.CONCAT(_xlfn._xlws.FILTER(F:F,D:D=H3))</f>
-        <v>95021D04B2028E03750000041400670354010C0418010604FD017D0380006B0357010D04AE000404970222045B00FF032301070461010E046C021C040D027E035C02880399000304530069031300FD0308016303290215042F0218042E021704F800050459021A0444028603690171032A02160463026F0313016E0349006603CD018203CF016A03D002D30445028703CA022404AB00650336021904D102D104A4021F04580285036B021B04C2022004A60290030D00FC032E00800348016D0378008403D3010F04C0028F03820001048F000204FB0110044C00FE039D021E0496022504C902230422021104710175035202210437010804FA006C0312007F0323006803ED02D504EE02D604EF02D704AF02F303</v>
+        <v>95021D04B2028E03750000041400670354010C0418010604FD017D0380006B0357010D04AE000404970222045B00FF032301070461010E046C021C040D027E035C02880399000304530069031300FD0308016303290215042F0218042E021704F800050459021A0444028603690171032A02160463026F0313016E0349006603CD018203CF016A03D002D30445028703CA022404AB00650336021904D102D104A4021F04580285036B021B04C2022004A60290030D00FC032E00800348016D0378008403D3010F04C0028F03820001048F000204FB0110044C00FE039D021E0496022504C902230422021104710175035202210437010804FA006C0312007F0323006803ED02D504EE02D604EF02D704AF02D8042200D904</v>
       </c>
       <c r="K3">
         <f t="shared" si="0"/>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L3">
         <f>K3*4</f>
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="M3" t="str">
         <f>DEC2HEX(L3)</f>
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="N3" s="20" t="s">
-        <v>1348</v>
+        <v>1343</v>
       </c>
       <c r="O3" t="str">
         <f>DEC2HEX(K3)</f>
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -5432,7 +5433,7 @@
       </c>
       <c r="N4" t="str">
         <f>DEC2HEX(HEX2DEC(N3)+L3,8)</f>
-        <v>00145064</v>
+        <v>00145068</v>
       </c>
       <c r="O4" t="str">
         <f>DEC2HEX(K4)</f>
@@ -5485,7 +5486,7 @@
       </c>
       <c r="N5" t="str">
         <f t="shared" ref="N5:N6" si="3">DEC2HEX(HEX2DEC(N4)+L4,8)</f>
-        <v>00145078</v>
+        <v>0014507C</v>
       </c>
       <c r="O5" t="str">
         <f>DEC2HEX(K5)</f>
@@ -5538,7 +5539,7 @@
       </c>
       <c r="N6" t="str">
         <f t="shared" si="3"/>
-        <v>00145080</v>
+        <v>00145084</v>
       </c>
       <c r="O6" t="str">
         <f>DEC2HEX(K6)</f>
@@ -5568,11 +5569,11 @@
       </c>
       <c r="L7">
         <f>SUM(L3:L6)</f>
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="M7" t="str">
         <f t="shared" si="2"/>
-        <v>138</v>
+        <v>13C</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -7126,13 +7127,13 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="B78" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="C78" s="17" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -7147,13 +7148,13 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" t="s">
-        <v>1343</v>
+        <v>1339</v>
       </c>
       <c r="B79" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="C79" t="s">
-        <v>1341</v>
+        <v>1337</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -7168,13 +7169,13 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>1344</v>
+        <v>1340</v>
       </c>
       <c r="B80" t="s">
-        <v>1340</v>
+        <v>1336</v>
       </c>
       <c r="C80" t="s">
-        <v>1342</v>
+        <v>1338</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -7195,17 +7196,38 @@
         <v>1123</v>
       </c>
       <c r="C81" t="s">
-        <v>1346</v>
+        <v>1342</v>
       </c>
       <c r="D81">
         <v>1</v>
       </c>
       <c r="E81" t="s">
-        <v>1345</v>
+        <v>1341</v>
       </c>
       <c r="F81" t="str">
-        <f t="shared" ref="F81" si="8">_xlfn.CONCAT(C81,A81)</f>
-        <v>AF02F303</v>
+        <f t="shared" ref="F81:F82" si="8">_xlfn.CONCAT(C81,A81)</f>
+        <v>AF02D804</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B82" t="s">
+        <v>489</v>
+      </c>
+      <c r="C82">
+        <v>2200</v>
+      </c>
+      <c r="D82">
+        <v>1</v>
+      </c>
+      <c r="E82" t="s">
+        <v>1344</v>
+      </c>
+      <c r="F82" t="str">
+        <f t="shared" si="8"/>
+        <v>2200D904</v>
       </c>
     </row>
   </sheetData>

--- a/ARM Functions/Other Mechanics/Move Alternate Animations Mine.xlsx
+++ b/ARM Functions/Other Mechanics/Move Alternate Animations Mine.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Other Mechanics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{433F565F-4F72-461B-BE80-D84816DD965B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{168533A8-176E-4027-8C59-271FF722006C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16457" windowHeight="17914" activeTab="1" xr2:uid="{664BA6B8-043A-4EF3-A83B-BDEF02BD0490}"/>
+    <workbookView xWindow="-16457" yWindow="0" windowWidth="16457" windowHeight="17914" xr2:uid="{664BA6B8-043A-4EF3-A83B-BDEF02BD0490}"/>
   </bookViews>
   <sheets>
     <sheet name="new function" sheetId="4" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="list of stock moves" sheetId="6" r:id="rId3"/>
     <sheet name="Original" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1" iterateCount="5"/>
+  <calcPr calcId="191029" iterate="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1627" uniqueCount="1349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1633" uniqueCount="1352">
   <si>
     <t>notes</t>
   </si>
@@ -4092,22 +4092,31 @@
     <t>AF02</t>
   </si>
   <si>
-    <t>00144F50</t>
-  </si>
-  <si>
     <t>Mega, Pulverizing Pancake</t>
   </si>
   <si>
     <t>offset to end of special sequences, set this manually, enter dec final file</t>
   </si>
   <si>
-    <t>4650A003</t>
-  </si>
-  <si>
     <t>D804</t>
   </si>
   <si>
     <t>D904</t>
+  </si>
+  <si>
+    <t>6C02</t>
+  </si>
+  <si>
+    <t>Hax</t>
+  </si>
+  <si>
+    <t>F802</t>
+  </si>
+  <si>
+    <t>00148F50</t>
+  </si>
+  <si>
+    <t>DA04</t>
   </si>
 </sst>
 </file>
@@ -4566,10 +4575,10 @@
   <cols>
     <col min="1" max="1" width="10.85546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="10.0703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.78515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="45.92578125" style="1" customWidth="1"/>
     <col min="5" max="8" width="9.2109375" style="1"/>
-    <col min="9" max="11" width="2.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="2.2109375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9.2109375" style="1"/>
   </cols>
   <sheetData>
@@ -4839,12 +4848,13 @@
         <f t="shared" si="0"/>
         <v>00077668</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>1346</v>
+      <c r="B19" s="7" t="str">
+        <f>_xlfn.CONCAT(RIGHT(C19,2),"50A003")</f>
+        <v>4850A003</v>
       </c>
       <c r="C19" s="6" t="str">
         <f>_xlfn.CONCAT("moveq r5, 0x",_xlfn.XLOOKUP(VALUE(MID(D18,4,1)),'Table Builder'!H:H,'Table Builder'!O:O))</f>
-        <v>moveq r5, 0x46</v>
+        <v>moveq r5, 0x48</v>
       </c>
       <c r="D19" s="6"/>
     </row>
@@ -5178,13 +5188,13 @@
       </c>
       <c r="B41" s="1" t="str">
         <f>_xlfn.LET(_xlpm.x,DEC2HEX(C41-800,4),RIGHT(_xlpm.x,2)&amp;LEFT(_xlpm.x,2)&amp;REPT(0,4))</f>
-        <v>B9010000</v>
+        <v>BA010000</v>
       </c>
       <c r="C41" s="1">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -5244,12 +5254,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F350D40E-C5C1-4F0A-9BA0-EE14E6CE8D22}">
-  <dimension ref="A1:O82"/>
+  <dimension ref="A1:O84"/>
   <sheetFormatPr defaultRowHeight="14.15"/>
   <cols>
     <col min="1" max="1" width="6.35546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.2109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.2109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.640625" customWidth="1"/>
     <col min="10" max="10" width="14.5" customWidth="1"/>
@@ -5361,30 +5371,30 @@
       </c>
       <c r="I3">
         <f>COUNTIF(D:D,"="&amp;H3)</f>
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J3" s="19" t="str" cm="1">
         <f t="array" ref="J3">_xlfn.CONCAT(_xlfn._xlws.FILTER(F:F,D:D=H3))</f>
-        <v>95021D04B2028E03750000041400670354010C0418010604FD017D0380006B0357010D04AE000404970222045B00FF032301070461010E046C021C040D027E035C02880399000304530069031300FD0308016303290215042F0218042E021704F800050459021A0444028603690171032A02160463026F0313016E0349006603CD018203CF016A03D002D30445028703CA022404AB00650336021904D102D104A4021F04580285036B021B04C2022004A60290030D00FC032E00800348016D0378008403D3010F04C0028F03820001048F000204FB0110044C00FE039D021E0496022504C902230422021104710175035202210437010804FA006C0312007F0323006803ED02D504EE02D604EF02D704AF02D8042200D904</v>
+        <v>95021D04B2028E03750000041400670354010C0418010604FD017D0380006B0357010D04AE000404970222045B00FF032301070461010E046C021C040D027E035C02880399000304530069031300FD0308016303290215042F0218042E021704F800050459021A0444028603690171032A02160463026F0313016E0349006603CD018203CF016A03D002D30445028703CA022404AB00650336021904D102D104A4021F04580285036B021B04C2022004A60290030D00FC032E00800348016D0378008403D3010F04C0028F03820001048F000204FB0110044C00FE039D021E0496022504C902230422021104710175035202210437010804FA006C0312007F0323006803ED02D504EE02D604EF02D704AF02D8042200D90430026C02F802DA04</v>
       </c>
       <c r="K3">
         <f t="shared" si="0"/>
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L3">
         <f>K3*4</f>
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="M3" t="str">
         <f>DEC2HEX(L3)</f>
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N3" s="20" t="s">
-        <v>1343</v>
+        <v>1350</v>
       </c>
       <c r="O3" t="str">
         <f>DEC2HEX(K3)</f>
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -5433,7 +5443,7 @@
       </c>
       <c r="N4" t="str">
         <f>DEC2HEX(HEX2DEC(N3)+L3,8)</f>
-        <v>00145068</v>
+        <v>00149070</v>
       </c>
       <c r="O4" t="str">
         <f>DEC2HEX(K4)</f>
@@ -5486,7 +5496,7 @@
       </c>
       <c r="N5" t="str">
         <f t="shared" ref="N5:N6" si="3">DEC2HEX(HEX2DEC(N4)+L4,8)</f>
-        <v>0014507C</v>
+        <v>00149084</v>
       </c>
       <c r="O5" t="str">
         <f>DEC2HEX(K5)</f>
@@ -5539,7 +5549,7 @@
       </c>
       <c r="N6" t="str">
         <f t="shared" si="3"/>
-        <v>00145084</v>
+        <v>0014908C</v>
       </c>
       <c r="O6" t="str">
         <f>DEC2HEX(K6)</f>
@@ -5569,11 +5579,11 @@
       </c>
       <c r="L7">
         <f>SUM(L3:L6)</f>
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="M7" t="str">
         <f t="shared" si="2"/>
-        <v>13C</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -7190,7 +7200,7 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="B81" t="s">
         <v>1123</v>
@@ -7205,13 +7215,13 @@
         <v>1341</v>
       </c>
       <c r="F81" t="str">
-        <f t="shared" ref="F81:F82" si="8">_xlfn.CONCAT(C81,A81)</f>
+        <f t="shared" ref="F81:F83" si="8">_xlfn.CONCAT(C81,A81)</f>
         <v>AF02D804</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="B82" t="s">
         <v>489</v>
@@ -7223,11 +7233,53 @@
         <v>1</v>
       </c>
       <c r="E82" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="F82" t="str">
         <f t="shared" si="8"/>
         <v>2200D904</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B83" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C83">
+        <v>3002</v>
+      </c>
+      <c r="D83">
+        <v>1</v>
+      </c>
+      <c r="E83" t="s">
+        <v>1074</v>
+      </c>
+      <c r="F83" t="str">
+        <f t="shared" si="8"/>
+        <v>30026C02</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B84" t="s">
+        <v>1348</v>
+      </c>
+      <c r="C84" t="s">
+        <v>1349</v>
+      </c>
+      <c r="D84">
+        <v>1</v>
+      </c>
+      <c r="E84" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F84" t="str">
+        <f t="shared" ref="F84" si="9">_xlfn.CONCAT(C84,A84)</f>
+        <v>F802DA04</v>
       </c>
     </row>
   </sheetData>
@@ -18907,10 +18959,10 @@
   <cols>
     <col min="1" max="1" width="10.85546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="10.0703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.78515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="29.2109375" style="1" customWidth="1"/>
     <col min="5" max="8" width="9.2109375" style="1"/>
-    <col min="9" max="11" width="2.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="2.2109375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9.2109375" style="1"/>
   </cols>
   <sheetData>
